--- a/MainTop/28.099.2026 Таня Озон/print_print_sorted.xlsx
+++ b/MainTop/28.099.2026 Таня Озон/print_print_sorted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\28.099.2026 Таня Озон\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E97D12CA-BC92-4158-BC6D-7708F3B0A03C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C388940C-AB31-4FA4-A55F-D81BF11FB3FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
